--- a/src/similarity_optimizer_test/sim123_t_swap_r_k_tot.xlsx
+++ b/src/similarity_optimizer_test/sim123_t_swap_r_k_tot.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,132 +462,132 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.33333333333333</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06136363636363636</v>
+        <v>0.03818181818181818</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06857142857142857</v>
+        <v>0.04857142857142857</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="B3" t="n">
-        <v>19.33333333333333</v>
+        <v>19.66666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07301587301587301</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09079365079365079</v>
+        <v>0.02857142857142857</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="B4" t="n">
-        <v>20.16666666666667</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04444444444444444</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.02857142857142857</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>750</v>
+        <v>300</v>
       </c>
       <c r="B5" t="n">
-        <v>19.33333333333333</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.375</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07301587301587301</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09079365079365079</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="B6" t="n">
-        <v>20.33333333333333</v>
+        <v>19.5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5</v>
       </c>
       <c r="D6" t="n">
         <v>0.02857142857142857</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.02857142857142857</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="B7" t="n">
-        <v>19.33333333333333</v>
+        <v>19.5</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5625</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07301587301587301</v>
+        <v>0.025</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09079365079365079</v>
+        <v>0.02857142857142857</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="B8" t="n">
-        <v>19.66666666666667</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E8" t="n">
-        <v>0.075</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1750</v>
+        <v>700</v>
       </c>
       <c r="B9" t="n">
-        <v>19.83333333333333</v>
+        <v>18.5</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04444444444444444</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="E9" t="n">
         <v>0.05</v>
@@ -595,563 +595,733 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="B10" t="n">
-        <v>20.33333333333333</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>0.375</v>
+        <v>0.45</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02857142857142857</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2250</v>
+        <v>900</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07714285714285714</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08888888888888888</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="B12" t="n">
-        <v>20.16666666666667</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04444444444444444</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.02857142857142857</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2750</v>
+        <v>1100</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04444444444444444</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="E13" t="n">
-        <v>0.04</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="B14" t="n">
-        <v>20.33333333333333</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="C14" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="D14" t="n">
         <v>0.02857142857142857</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3250</v>
+        <v>1300</v>
       </c>
       <c r="B15" t="n">
-        <v>19.33333333333333</v>
+        <v>20.33333333333333</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5625</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07301587301587301</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09079365079365079</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3500</v>
+        <v>1400</v>
       </c>
       <c r="B16" t="n">
-        <v>21.16666666666667</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="D16" t="n">
-        <v>0.07714285714285714</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E16" t="n">
-        <v>0.08888888888888888</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3750</v>
+        <v>1500</v>
       </c>
       <c r="B17" t="n">
-        <v>20.66666666666667</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4000</v>
+        <v>1600</v>
       </c>
       <c r="B18" t="n">
-        <v>21.16666666666667</v>
+        <v>20.5</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="D18" t="n">
-        <v>0.07714285714285714</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08888888888888888</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4250</v>
+        <v>1700</v>
       </c>
       <c r="B19" t="n">
-        <v>20.16666666666667</v>
+        <v>20.5</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.07936507936507936</v>
+        <v>0.04444444444444444</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09079365079365079</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4500</v>
+        <v>1800</v>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07714285714285714</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08888888888888888</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4750</v>
+        <v>1900</v>
       </c>
       <c r="B21" t="n">
-        <v>21.16666666666667</v>
+        <v>20.33333333333333</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="D21" t="n">
-        <v>0.07714285714285714</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08888888888888888</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="B22" t="n">
-        <v>21.16666666666667</v>
+        <v>19.66666666666667</v>
       </c>
       <c r="C22" t="n">
         <v>0.5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07714285714285714</v>
+        <v>0.0404040404040404</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08888888888888888</v>
+        <v>0.05357142857142857</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5250</v>
+        <v>2100</v>
       </c>
       <c r="B23" t="n">
-        <v>20.5</v>
+        <v>19.66666666666667</v>
       </c>
       <c r="C23" t="n">
-        <v>0.55</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="D23" t="n">
         <v>0.02857142857142857</v>
       </c>
       <c r="E23" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.02857142857142857</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5500</v>
+        <v>2200</v>
       </c>
       <c r="B24" t="n">
-        <v>21.16666666666667</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.375</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07714285714285714</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08888888888888888</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5750</v>
+        <v>2300</v>
       </c>
       <c r="B25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="D25" t="n">
-        <v>0.07714285714285714</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08888888888888888</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6000</v>
+        <v>2400</v>
       </c>
       <c r="B26" t="n">
-        <v>21.16666666666667</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.375</v>
       </c>
       <c r="D26" t="n">
-        <v>0.07714285714285714</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08888888888888888</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6250</v>
+        <v>2500</v>
       </c>
       <c r="B27" t="n">
-        <v>19.33333333333333</v>
+        <v>19</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5625</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="D27" t="n">
-        <v>0.07301587301587301</v>
+        <v>0.04722222222222222</v>
       </c>
       <c r="E27" t="n">
-        <v>0.09079365079365079</v>
+        <v>0.05357142857142857</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6500</v>
+        <v>2600</v>
       </c>
       <c r="B28" t="n">
-        <v>19.83333333333333</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="C28" t="n">
-        <v>0.375</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02857142857142857</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6750</v>
+        <v>2700</v>
       </c>
       <c r="B29" t="n">
-        <v>20.16666666666667</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="D29" t="n">
-        <v>0.04444444444444444</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E29" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>7000</v>
+        <v>2800</v>
       </c>
       <c r="B30" t="n">
-        <v>20.16666666666667</v>
+        <v>20.33333333333333</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="D30" t="n">
-        <v>0.05714285714285714</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="E30" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>7250</v>
+        <v>2900</v>
       </c>
       <c r="B31" t="n">
-        <v>19.33333333333333</v>
+        <v>20.33333333333333</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D31" t="n">
-        <v>0.07301587301587301</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E31" t="n">
-        <v>0.09079365079365079</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>7500</v>
+        <v>3000</v>
       </c>
       <c r="B32" t="n">
-        <v>20.33333333333333</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02857142857142857</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>7750</v>
+        <v>3100</v>
       </c>
       <c r="B33" t="n">
-        <v>19.33333333333333</v>
+        <v>20.66666666666667</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5625</v>
+        <v>0.375</v>
       </c>
       <c r="D33" t="n">
-        <v>0.07301587301587301</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E33" t="n">
-        <v>0.09079365079365079</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>8000</v>
+        <v>3200</v>
       </c>
       <c r="B34" t="n">
-        <v>19.66666666666667</v>
+        <v>20</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="D34" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E34" t="n">
-        <v>0.075</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>8250</v>
+        <v>3300</v>
       </c>
       <c r="B35" t="n">
-        <v>19.66666666666667</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="D35" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E35" t="n">
-        <v>0.075</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>8500</v>
+        <v>3400</v>
       </c>
       <c r="B36" t="n">
-        <v>19.83333333333333</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.35</v>
       </c>
       <c r="D36" t="n">
-        <v>0.04444444444444444</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="E36" t="n">
-        <v>0.05</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>8750</v>
+        <v>3500</v>
       </c>
       <c r="B37" t="n">
-        <v>21.16666666666667</v>
+        <v>19.66666666666667</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="D37" t="n">
-        <v>0.07714285714285714</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E37" t="n">
-        <v>0.08888888888888888</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>9000</v>
+        <v>3600</v>
       </c>
       <c r="B38" t="n">
-        <v>19.83333333333333</v>
+        <v>19.5</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.5</v>
       </c>
       <c r="D38" t="n">
-        <v>0.04444444444444444</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="E38" t="n">
-        <v>0.05</v>
+        <v>0.02857142857142857</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>9250</v>
+        <v>3700</v>
       </c>
       <c r="B39" t="n">
-        <v>19.33333333333333</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="D39" t="n">
-        <v>0.07301587301587301</v>
+        <v>0.04444444444444444</v>
       </c>
       <c r="E39" t="n">
-        <v>0.09079365079365079</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>9500</v>
+        <v>3800</v>
       </c>
       <c r="B40" t="n">
-        <v>20.5</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="C40" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="D40" t="n">
         <v>0.02857142857142857</v>
       </c>
       <c r="E40" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>9750</v>
+        <v>3900</v>
       </c>
       <c r="B41" t="n">
-        <v>21.16666666666667</v>
+        <v>19.66666666666667</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="D41" t="n">
-        <v>0.07714285714285714</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="E41" t="n">
-        <v>0.08888888888888888</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="B42" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="D42" t="n">
-        <v>0.04444444444444444</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="E42" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4100</v>
+      </c>
+      <c r="B43" t="n">
+        <v>19.33333333333333</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4200</v>
+      </c>
+      <c r="B44" t="n">
+        <v>19.66666666666667</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.0404040404040404</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.05357142857142857</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4300</v>
+      </c>
+      <c r="B45" t="n">
+        <v>19.33333333333333</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4400</v>
+      </c>
+      <c r="B46" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.04444444444444444</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4500</v>
+      </c>
+      <c r="B47" t="n">
+        <v>20</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.02222222222222222</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4600</v>
+      </c>
+      <c r="B48" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.04444444444444444</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4700</v>
+      </c>
+      <c r="B49" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4800</v>
+      </c>
+      <c r="B50" t="n">
+        <v>18.83333333333333</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4900</v>
+      </c>
+      <c r="B51" t="n">
+        <v>19.83333333333333</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.02222222222222222</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B52" t="n">
+        <v>19.66666666666667</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.0404040404040404</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.05357142857142857</v>
       </c>
     </row>
   </sheetData>
